--- a/data/trans_dic/IP09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 54,28</t>
+          <t>7,14; 58,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 50,65</t>
+          <t>19,04; 52,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,41; 74,47</t>
+          <t>26,03; 75,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 58,05</t>
+          <t>6,75; 59,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,73; 50,98</t>
+          <t>12,91; 51,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 46,47</t>
+          <t>16,05; 45,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 47,39</t>
+          <t>8,32; 46,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,64</t>
+          <t>0,0; 39,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 44,66</t>
+          <t>15,73; 44,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 44,08</t>
+          <t>20,97; 43,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 52,86</t>
+          <t>19,97; 53,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 34,48</t>
+          <t>5,6; 35,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 35,15</t>
+          <t>5,28; 31,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 47,39</t>
+          <t>18,34; 46,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 53,58</t>
+          <t>17,24; 52,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,09; 78,17</t>
+          <t>27,58; 75,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 34,23</t>
+          <t>11,25; 34,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 38,21</t>
+          <t>14,15; 38,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,89; 73,14</t>
+          <t>35,18; 72,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 53,94</t>
+          <t>21,57; 53,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 28,31</t>
+          <t>12,07; 28,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,44; 37,47</t>
+          <t>19,25; 38,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,86; 57,45</t>
+          <t>33,76; 57,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 55,32</t>
+          <t>26,96; 55,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 46,53</t>
+          <t>9,71; 48,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 55,15</t>
+          <t>17,38; 53,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 70,33</t>
+          <t>14,75; 69,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,91; 68,79</t>
+          <t>25,78; 67,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,08; 63,59</t>
+          <t>22,61; 63,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 45,55</t>
+          <t>9,26; 47,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,57; 100,0</t>
+          <t>37,92; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,55; 61,66</t>
+          <t>24,85; 63,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,99; 49,41</t>
+          <t>20,27; 48,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,21; 45,59</t>
+          <t>17,96; 44,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,23; 76,25</t>
+          <t>32,61; 76,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,4; 58,57</t>
+          <t>29,62; 57,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 65,57</t>
+          <t>7,7; 58,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,58; 62,75</t>
+          <t>20,49; 64,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,72; 71,25</t>
+          <t>20,88; 72,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 66,43</t>
+          <t>9,18; 63,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 54,98</t>
+          <t>18,45; 52,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,37; 70,81</t>
+          <t>37,66; 72,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 64,46</t>
+          <t>18,27; 64,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 41,91</t>
+          <t>9,08; 43,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 47,89</t>
+          <t>19,88; 49,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 63,0</t>
+          <t>36,68; 63,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,82; 60,76</t>
+          <t>24,14; 56,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 49,05</t>
+          <t>15,39; 47,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 32,43</t>
+          <t>15,2; 33,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,84</t>
+          <t>26,84; 43,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 52,38</t>
+          <t>29,11; 51,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,7; 56,99</t>
+          <t>27,69; 58,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 36,82</t>
+          <t>21,42; 37,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,65</t>
+          <t>26,02; 41,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 58,14</t>
+          <t>34,37; 56,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,61; 39,25</t>
+          <t>19,14; 39,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 33,06</t>
+          <t>20,57; 32,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,34</t>
+          <t>28,31; 40,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,85; 52,0</t>
+          <t>34,9; 50,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,58</t>
+          <t>25,88; 43,54</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7344</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7543</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14286</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3077</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>715; 5879</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4000; 10944</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2521; 7352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>500; 4375</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2005; 8023</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4003; 11348</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1051; 5855</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4546</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4016; 11410</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9635; 19931</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4457; 11906</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1056; 6781</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3945</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11709</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8277</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11346</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18727</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17905</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13072</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1303; 7748</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5189; 13180</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3191; 9642</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2563; 7011</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3955; 12067</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5438; 14712</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7412; 15352</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4887; 12128</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7218; 16955</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>12839; 25568</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13365; 22776</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8615; 17577</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7716</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9578</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>17517</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1331; 6581</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3511; 10798</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1236; 5855</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4316; 11347</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3400; 9554</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1385; 7056</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2249; 5931</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5822; 14916</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5824; 13868</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6315; 15672</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4667; 11011</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11898; 23116</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9341</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8375</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18844</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9219</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>19836</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>606; 4590</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2740; 8581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2202; 7642</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2694; 18675</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3279; 9332</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9076; 17438</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2159; 7632</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3768; 18030</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5098; 12588</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>13746; 23742</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5397; 12724</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10900; 33674</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28397</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>36842</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>62649</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42852</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>53502</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>8551; 18823</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22240; 35877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13716; 24245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17385; 37000</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17885; 31518</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26651; 42342</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17685; 29248</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>18953; 38918</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>28746; 45033</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>52464; 74221</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>34396; 50248</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>41883; 70448</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 58,76</t>
+          <t>10,16; 59,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 52,09</t>
+          <t>18,9; 49,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 75,93</t>
+          <t>25,02; 75,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 59,07</t>
+          <t>10,18; 62,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 51,66</t>
+          <t>16,16; 51,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 45,5</t>
+          <t>15,88; 45,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 46,36</t>
+          <t>8,72; 44,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,71</t>
+          <t>0,0; 33,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 44,68</t>
+          <t>15,22; 43,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 43,38</t>
+          <t>20,62; 42,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 53,36</t>
+          <t>20,42; 52,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 35,96</t>
+          <t>6,29; 33,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 31,41</t>
+          <t>7,24; 31,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 46,59</t>
+          <t>19,21; 49,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 52,08</t>
+          <t>18,2; 54,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,58; 75,45</t>
+          <t>28,25; 76,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 34,34</t>
+          <t>11,63; 35,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 38,29</t>
+          <t>14,97; 39,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,18; 72,86</t>
+          <t>36,44; 71,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,57; 53,53</t>
+          <t>20,86; 52,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,07; 28,35</t>
+          <t>11,8; 28,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 38,33</t>
+          <t>19,63; 38,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,76; 57,54</t>
+          <t>32,81; 59,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,96; 55,01</t>
+          <t>28,61; 54,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 48,04</t>
+          <t>9,75; 48,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 53,46</t>
+          <t>19,03; 54,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 69,88</t>
+          <t>13,89; 71,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,78; 67,79</t>
+          <t>24,83; 67,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 63,53</t>
+          <t>22,04; 64,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 47,16</t>
+          <t>9,5; 47,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,92; 100,0</t>
+          <t>38,27; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 63,66</t>
+          <t>23,08; 62,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,27; 48,26</t>
+          <t>20,45; 48,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,96; 44,57</t>
+          <t>19,58; 45,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,61; 76,95</t>
+          <t>33,95; 77,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 57,55</t>
+          <t>29,59; 59,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 58,3</t>
+          <t>7,89; 64,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,49; 64,16</t>
+          <t>20,55; 65,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,88; 72,47</t>
+          <t>21,21; 71,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 63,64</t>
+          <t>10,77; 65,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 52,52</t>
+          <t>18,3; 52,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,66; 72,36</t>
+          <t>36,3; 69,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 64,59</t>
+          <t>17,72; 64,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 43,45</t>
+          <t>10,15; 44,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 49,09</t>
+          <t>17,71; 48,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 63,36</t>
+          <t>37,84; 63,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 56,9</t>
+          <t>24,8; 59,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 47,54</t>
+          <t>14,82; 44,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,2; 33,47</t>
+          <t>14,64; 33,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 43,29</t>
+          <t>26,58; 43,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 51,45</t>
+          <t>29,7; 52,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,69; 58,93</t>
+          <t>27,16; 56,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 37,76</t>
+          <t>21,85; 38,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,02; 41,34</t>
+          <t>26,19; 41,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 56,85</t>
+          <t>35,03; 57,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 39,3</t>
+          <t>20,14; 40,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,57; 32,23</t>
+          <t>20,38; 33,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,06</t>
+          <t>28,71; 40,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,9; 50,98</t>
+          <t>35,99; 52,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,54</t>
+          <t>24,71; 42,72</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>715; 5879</t>
+          <t>1016; 5961</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4000; 10944</t>
+          <t>3970; 10420</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2521; 7352</t>
+          <t>2423; 7286</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500; 4375</t>
+          <t>754; 4617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2005; 8023</t>
+          <t>2509; 7945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4003; 11348</t>
+          <t>3960; 11245</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1051; 5855</t>
+          <t>1101; 5643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4546</t>
+          <t>0; 3874</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4016; 11410</t>
+          <t>3885; 11156</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9635; 19931</t>
+          <t>9475; 19557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4457; 11906</t>
+          <t>4555; 11747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1056; 6781</t>
+          <t>1186; 6406</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1303; 7748</t>
+          <t>1786; 7762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5189; 13180</t>
+          <t>5433; 13944</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3191; 9642</t>
+          <t>3370; 10025</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2563; 7011</t>
+          <t>2625; 7062</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3955; 12067</t>
+          <t>4086; 12348</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5438; 14712</t>
+          <t>5750; 15043</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7412; 15352</t>
+          <t>7677; 15108</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4887; 12128</t>
+          <t>4727; 11987</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7218; 16955</t>
+          <t>7059; 16852</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12839; 25568</t>
+          <t>13094; 25621</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13365; 22776</t>
+          <t>12989; 23473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8615; 17577</t>
+          <t>9142; 17411</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1331; 6581</t>
+          <t>1335; 6710</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3511; 10798</t>
+          <t>3845; 10950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1236; 5855</t>
+          <t>1164; 5987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4316; 11347</t>
+          <t>4157; 11313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3400; 9554</t>
+          <t>3315; 9743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1385; 7056</t>
+          <t>1422; 7087</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2249; 5931</t>
+          <t>2270; 5931</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5822; 14916</t>
+          <t>5407; 14725</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5824; 13868</t>
+          <t>5876; 13838</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6315; 15672</t>
+          <t>6885; 15978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4667; 11011</t>
+          <t>4858; 11032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11898; 23116</t>
+          <t>11884; 24001</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>606; 4590</t>
+          <t>621; 5053</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2740; 8581</t>
+          <t>2748; 8779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2202; 7642</t>
+          <t>2236; 7538</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2694; 18675</t>
+          <t>3161; 19252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3279; 9332</t>
+          <t>3251; 9289</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9076; 17438</t>
+          <t>8747; 16837</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2159; 7632</t>
+          <t>2094; 7580</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3768; 18030</t>
+          <t>4210; 18530</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5098; 12588</t>
+          <t>4541; 12355</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13746; 23742</t>
+          <t>14180; 23752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5397; 12724</t>
+          <t>5546; 13323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10900; 33674</t>
+          <t>10496; 31841</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8551; 18823</t>
+          <t>8235; 18927</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22240; 35877</t>
+          <t>22023; 35934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13716; 24245</t>
+          <t>13995; 24775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17385; 37000</t>
+          <t>17052; 35165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17885; 31518</t>
+          <t>18238; 31815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26651; 42342</t>
+          <t>26828; 42523</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17685; 29248</t>
+          <t>18024; 29737</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18953; 38918</t>
+          <t>19946; 39888</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28746; 45033</t>
+          <t>28478; 46224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52464; 74221</t>
+          <t>53194; 74540</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34396; 50248</t>
+          <t>35470; 51558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41883; 70448</t>
+          <t>39976; 69126</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>29,48%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>33,05%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>50,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,76%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 59,58</t>
+          <t>12,73; 50,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,9; 49,6</t>
+          <t>15,54; 46,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,02; 75,25</t>
+          <t>8,91; 47,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 62,33</t>
+          <t>0,0; 37,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 51,16</t>
+          <t>6,91; 54,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 45,09</t>
+          <t>17,99; 50,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 44,68</t>
+          <t>25,41; 74,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,84</t>
+          <t>7,91; 57,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 43,69</t>
+          <t>16,1; 44,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 42,56</t>
+          <t>20,73; 44,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,42; 52,65</t>
+          <t>21,25; 52,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 33,97</t>
+          <t>5,15; 34,43</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>16,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>31,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>33,47%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>55,57%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 31,47</t>
+          <t>11,7; 34,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 49,29</t>
+          <t>14,49; 38,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 54,14</t>
+          <t>36,89; 73,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 76,0</t>
+          <t>21,31; 54,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,63; 35,14</t>
+          <t>7,18; 35,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 39,15</t>
+          <t>18,81; 47,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,44; 71,71</t>
+          <t>18,44; 53,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 52,9</t>
+          <t>27,74; 79,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 28,18</t>
+          <t>11,62; 28,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,63; 38,41</t>
+          <t>19,44; 37,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,81; 59,3</t>
+          <t>32,86; 57,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 54,5</t>
+          <t>27,87; 56,26</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76,45%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44,19%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25,02%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>34,72%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,45%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 48,98</t>
+          <t>22,08; 63,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 54,21</t>
+          <t>9,12; 45,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 71,45</t>
+          <t>38,57; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 67,59</t>
+          <t>25,13; 64,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,04; 64,79</t>
+          <t>9,55; 46,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 47,37</t>
+          <t>18,22; 55,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,27; 100,0</t>
+          <t>14,54; 70,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,08; 62,85</t>
+          <t>25,72; 68,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,45; 48,15</t>
+          <t>18,99; 49,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,58; 45,44</t>
+          <t>20,21; 45,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,95; 77,1</t>
+          <t>33,23; 76,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,59; 59,75</t>
+          <t>31,58; 59,87</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 64,18</t>
+          <t>18,21; 54,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 65,64</t>
+          <t>36,37; 70,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 71,48</t>
+          <t>18,24; 64,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 65,6</t>
+          <t>10,52; 43,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 52,28</t>
+          <t>8,18; 65,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,3; 69,87</t>
+          <t>20,58; 62,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 64,15</t>
+          <t>19,72; 71,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 44,66</t>
+          <t>7,61; 34,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 48,18</t>
+          <t>19,82; 47,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,84; 63,38</t>
+          <t>37,0; 63,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,8; 59,58</t>
+          <t>24,82; 60,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 44,95</t>
+          <t>13,48; 36,07</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 33,65</t>
+          <t>21,67; 36,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,58; 43,36</t>
+          <t>26,05; 42,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 52,57</t>
+          <t>35,37; 58,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,16; 56,01</t>
+          <t>19,96; 40,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,85; 38,11</t>
+          <t>14,34; 32,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,52</t>
+          <t>26,05; 42,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,03; 57,8</t>
+          <t>29,68; 52,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 40,28</t>
+          <t>22,96; 42,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,38; 33,08</t>
+          <t>20,95; 33,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 40,23</t>
+          <t>28,93; 40,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 52,31</t>
+          <t>35,85; 52,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,71; 42,72</t>
+          <t>24,58; 39,54</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7344</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2949</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6942</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4854</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7344</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2762</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1016; 5961</t>
+          <t>1977; 7917</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3970; 10420</t>
+          <t>3876; 11589</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2423; 7286</t>
+          <t>1125; 5985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>754; 4617</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2509; 7945</t>
+          <t>692; 5431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3960; 11245</t>
+          <t>3780; 10641</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1101; 5643</t>
+          <t>2461; 7210</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3874</t>
+          <t>552; 4009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3885; 11156</t>
+          <t>4110; 11405</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9475; 19557</t>
+          <t>9525; 20254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4555; 11747</t>
+          <t>4741; 11794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1186; 6406</t>
+          <t>844; 5638</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11709</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6983</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3945</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8960</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6197</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9767</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11709</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>11584</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1786; 7762</t>
+          <t>4111; 12028</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5433; 13944</t>
+          <t>5566; 14680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3370; 10025</t>
+          <t>7772; 15410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2625; 7062</t>
+          <t>4029; 10274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4086; 12348</t>
+          <t>1772; 8669</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5750; 15043</t>
+          <t>5320; 13406</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7677; 15108</t>
+          <t>3414; 9921</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4727; 11987</t>
+          <t>2466; 7031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7059; 16852</t>
+          <t>6949; 16932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13094; 25621</t>
+          <t>12966; 24996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12989; 23473</t>
+          <t>13008; 22741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9142; 17411</t>
+          <t>7745; 15635</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9523</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3427</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7013</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3337</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6151</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17383</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1335; 6710</t>
+          <t>3320; 9563</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3845; 10950</t>
+          <t>1365; 6815</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1164; 5987</t>
+          <t>2288; 5931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4157; 11313</t>
+          <t>5417; 13907</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3315; 9743</t>
+          <t>1308; 6374</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1422; 7087</t>
+          <t>3680; 11140</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2270; 5931</t>
+          <t>1218; 5893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5407; 14725</t>
+          <t>4390; 11724</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5876; 13838</t>
+          <t>5457; 14198</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6885; 15978</t>
+          <t>7107; 16030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4858; 11032</t>
+          <t>4755; 10911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11884; 24001</t>
+          <t>12197; 23119</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2479</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5482</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4688</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9341</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13362</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4531</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>15063</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>621; 5053</t>
+          <t>3236; 9769</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2748; 8779</t>
+          <t>8765; 17064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2236; 7538</t>
+          <t>2156; 7616</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3161; 19252</t>
+          <t>4106; 16825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3251; 9289</t>
+          <t>644; 5163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8747; 16837</t>
+          <t>2752; 8393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2094; 7580</t>
+          <t>2079; 7513</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4210; 18530</t>
+          <t>1929; 8857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4541; 12355</t>
+          <t>5082; 12281</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14180; 23752</t>
+          <t>13866; 23608</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5546; 13323</t>
+          <t>5549; 13586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10496; 31841</t>
+          <t>8672; 23211</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8235; 18927</t>
+          <t>18092; 30739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22023; 35934</t>
+          <t>26680; 43680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13995; 24775</t>
+          <t>18195; 29911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17052; 35165</t>
+          <t>17739; 36240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18238; 31815</t>
+          <t>8067; 18237</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26828; 42523</t>
+          <t>21589; 35499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18024; 29737</t>
+          <t>13988; 24681</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19946; 39888</t>
+          <t>13376; 24933</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28478; 46224</t>
+          <t>29266; 46196</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53194; 74540</t>
+          <t>53598; 74753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35470; 51558</t>
+          <t>35337; 51256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39976; 69126</t>
+          <t>36173; 58177</t>
         </is>
       </c>
     </row>
